--- a/data/catalog/catalog.xlsx
+++ b/data/catalog/catalog.xlsx
@@ -11,6 +11,7 @@
     <sheet name="baterias" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="helices" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="helices_tabela" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="tracao" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2558,4 +2559,180 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>x_var</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>y_var</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>gain</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>rho_exp</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>rho0</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>xmax</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ymax</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>p00</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>p10</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>p01</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>p20</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>p11</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>p02</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>p30</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>p21</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>p03</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>p40</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>p31</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>p22</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>p13</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>p04</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>p50</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>p41</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>p32</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>p23</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>p14</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>p05</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/catalog/catalog.xlsx
+++ b/data/catalog/catalog.xlsx
@@ -2567,7 +2567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2613,120 +2613,130 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>x_const</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>y_const</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>p00</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>p01</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>p20</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>p11</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>p02</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>p30</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>p21</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>p12</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>p03</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>p40</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>p31</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>p22</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>p13</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>p04</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>p50</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>p41</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>p32</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>p23</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>p14</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>p05</t>
         </is>
